--- a/site/exports/scu-west-china-pharmacy.xlsx
+++ b/site/exports/scu-west-china-pharmacy.xlsx
@@ -14,11 +14,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总览'!$A$1:$K$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'经历'!$A$1:$S$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'导师'!$A$1:$L$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'论文'!$A$1:$L$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'来源'!$A$1:$G$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总览'!$A$1:$K$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'经历'!$A$1:$S$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'导师'!$A$1:$L$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'论文'!$A$1:$L$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'来源'!$A$1:$G$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -453,8 +453,8 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="65" customWidth="1" min="6" max="6"/>
     <col width="37.8" customWidth="1" min="7" max="7"/>
-    <col width="26.6" customWidth="1" min="8" max="8"/>
-    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="40.59999999999999" customWidth="1" min="8" max="8"/>
+    <col width="23.8" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
   </cols>
@@ -477,7 +477,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>官方主页</t>
+          <t>个人主页／职业网站（来源类型见说明）</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -487,7 +487,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>缺项与冲突</t>
+          <t>来源说明与待核事项</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -502,7 +502,7 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>替代官方职业报道（非个人主页）</t>
+          <t>替代职业资料来源（非已核个人主页）</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -569,10 +569,118 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>宋振雷</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>校区未标注</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>华西药学院</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>https://pharmacy.scu.edu.cn/info/1058/1760.htm</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>未知（来源日期异常）</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>现职unknown，导航false；目录仅支持来源所述系归属。；本科及硕博连读2个教育事件均授位null；硕博连读不拆两个学位。；博士后是1个组合事件、2机构顺序；false只表示分析分类为非学位，转校时间及每校起止未知。；2条阶段师承不是正式论文导师；本人博士生导师资格不当本人师承。；页面发布日期不等于最后修改日期；无可靠实时人事状态。；2部官网书目均明确参编但未列作者串；不补作者名单，不外查metadata或全文。；目录姓名reader标签可见，但未点击回个人页，raw href及目录链接目标未另核。；来源单位：华西药学院/药物化学系。本站按“华西药学院”归组仅供展示，保留原单位标签；不据此认证法律行政层级、校区或当前任职。；来源记载职业信息：职业职称：教授 (博士生导师)。上述为留存来源职业表述，不作本轮当前任职或资格认证；指导他人的资格不新增本人导师关系。</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>官方资料（原来源）；公开个人页（访问与内容时效见来源记录）</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr"/>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>scu</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>四川大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>贾知军</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>校区未标注</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>华西药学院</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>https://pharmacy.scu.edu.cn/info/1064/1823.htm</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>未知（来源日期异常）</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>现职unknown，导航false；两个官网目录仅核来源所述归属。；本科、硕士、博士3项均无明确获授，授位null；所有授位日期及法律授位主体未知。；本科市场营销为第二专业，不推第二学位。；两段博士后非学位false是分析分类，不否定其他学位。；4条分别为硕士/博士/博士后阶段师承；正式学位论文导师仍未知。；目录“四川大学第二医院”原词保留，不自行规范为华西第二医院或确认联聘。；2篇论文只核官网所列标题、作者串、年份与刊物信息；星号不升级角色；外部metadata与全文未核。；页面发布日期非最后更新日期、毕业日期或授位日期。；目录本人链接label已观察，但未回点目标，原生href及链接目标仍未独立核验。；来源单位：华西药学院/生物技术药物学系。本站按“华西药学院”归组仅供展示，保留原单位标签；不据此认证法律行政层级、校区或当前任职。；来源记载职业信息：职业职称：研究员（博士生导师）。上述为留存来源职业表述，不作本轮当前任职或资格认证；指导他人的资格不新增本人导师关系。</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>官方资料（原来源）；公开个人页（访问与内容时效见来源记录）</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>scu</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>四川大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K2"/>
+  <autoFilter ref="A1:K4"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -584,13 +692,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S8"/>
+  <dimension ref="A1:S19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="16.8" customWidth="1" min="2" max="2"/>
+    <col width="53.2" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16.8" customWidth="1" min="4" max="4"/>
+    <col width="19.6" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
@@ -601,7 +709,7 @@
     <col width="16" customWidth="1" min="12" max="12"/>
     <col width="16" customWidth="1" min="13" max="13"/>
     <col width="16" customWidth="1" min="14" max="14"/>
-    <col width="53.2" customWidth="1" min="15" max="15"/>
+    <col width="65" customWidth="1" min="15" max="15"/>
     <col width="16" customWidth="1" min="16" max="16"/>
     <col width="64.39999999999999" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
@@ -666,7 +774,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>确证授位</t>
+          <t>来源记载学位</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
@@ -1166,8 +1274,721 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>宋振雷</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>education_stage_without_explicit_award</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>本科</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>兰州大学</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr"/>
+      <c r="I9" s="2" t="inlineStr"/>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" s="2" t="inlineStr"/>
+      <c r="N9" s="2" t="inlineStr"/>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>本科为学习阶段；未明确学位名称、毕业或获授，均不推断。；No explicit award wording in source; study label does not establish conferral.；本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。；来源department：化学系基地班；来源date_as_source：1996-2000</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr"/>
+      <c r="Q9" s="3" t="inlineStr">
+        <is>
+          <t>https://pharmacy.scu.edu.cn/info/1058/1760.htm</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>scu</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>四川大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>宋振雷</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>education_stage_without_explicit_award</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>硕博连读</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>兰州大学</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>有机化学</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr"/>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr"/>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr"/>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>一个合并学习阶段，不拆成硕士和博士两个已授学位；硕博分界、各阶段毕业及授位日期未知。；No explicit award wording in source; study label does not establish conferral.；本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。；来源department：化学系；来源date_as_source：2000-2005</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr"/>
+      <c r="Q10" s="3" t="inlineStr">
+        <is>
+          <t>https://pharmacy.scu.edu.cn/info/1058/1760.htm</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>scu</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>四川大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>宋振雷</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>postdoctoral_research</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>博士后</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr"/>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr"/>
+      <c r="I11" s="2" t="inlineStr"/>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr"/>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>同一组合叙述保留一个博士后经历，先在明尼苏达大学化学系后转至威斯康星大学麦迪逊分校药学院；转入时间和两地各自起止未知，不将全段分别赋给两校。；本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。；来源date_as_source：2005-2008</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr"/>
+      <c r="Q11" s="3" t="inlineStr">
+        <is>
+          <t>https://pharmacy.scu.edu.cn/info/1058/1760.htm</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>scu</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>四川大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>宋振雷</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>employment</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>副教授</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>四川大学</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr"/>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr"/>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr"/>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>Preserve source wording; an open interval does not establish current employment at retrieval.；任职按留存来源表述保留；不据此认证当前人事状态。；来源date_as_source：2008-2012；来源记载（单位）：华西药学院</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr"/>
+      <c r="Q12" s="3" t="inlineStr">
+        <is>
+          <t>https://pharmacy.scu.edu.cn/info/1058/1760.htm</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>scu</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>四川大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>宋振雷</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>employment</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>教授</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>四川大学</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr"/>
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr"/>
+      <c r="I13" s="2" t="inlineStr"/>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr"/>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr"/>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>Preserve source wording; an open interval does not establish current employment at retrieval.；任职按留存来源表述保留；不据此认证当前人事状态。；来源date_as_source：2012-至今；来源记载（单位）：华西药学院</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr"/>
+      <c r="Q13" s="3" t="inlineStr">
+        <is>
+          <t>https://pharmacy.scu.edu.cn/info/1058/1760.htm</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>scu</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>四川大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>贾知军</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>education_stage_without_explicit_award</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>博士</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>德国多特蒙德工业大学</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>化学生物学</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr"/>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr"/>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr"/>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>博士仅标签，无明确获授；学习结束年不作授位年。；No explicit award wording in source; study label does not establish conferral.；本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。；来源date_as_source：2012-2016</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr"/>
+      <c r="Q14" s="3" t="inlineStr">
+        <is>
+          <t>https://pharmacy.scu.edu.cn/info/1064/1823.htm</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>scu</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>四川大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>贾知军</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>education_stage_without_explicit_award</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>硕士</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>四川大学</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>药物化学</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr"/>
+      <c r="I15" s="2" t="inlineStr"/>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr"/>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr"/>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>硕士仅标签，无明确获授；学习结束年不作授位年。；No explicit award wording in source; study label does not establish conferral.；本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。；来源date_as_source：2009-2012</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr"/>
+      <c r="Q15" s="3" t="inlineStr">
+        <is>
+          <t>https://pharmacy.scu.edu.cn/info/1064/1823.htm</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>scu</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t>四川大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>贾知军</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>education_stage_without_explicit_award</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>本科</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>四川大学</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>生物技术基地班</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr"/>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr"/>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr"/>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>市场营销是原文“第二专业”，不升级成第二学位或另计本科事件。；No explicit award wording in source; study label does not establish conferral.；本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。；来源date_as_source：2005-2009；来源记载（additional_field_as_source）：市场营销（第二专业）</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr"/>
+      <c r="Q16" s="3" t="inlineStr">
+        <is>
+          <t>https://pharmacy.scu.edu.cn/info/1064/1823.htm</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>scu</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>四川大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>贾知军</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>postdoctoral_research</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>博士后</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>美国加州理工学院</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr"/>
+      <c r="I17" s="2" t="inlineStr"/>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr"/>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>博士后按非学位研究分类；不视作授予博士学位。；本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。；来源date_as_source：2018-2020</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr"/>
+      <c r="Q17" s="3" t="inlineStr">
+        <is>
+          <t>https://pharmacy.scu.edu.cn/info/1064/1823.htm</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>scu</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>四川大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>贾知军</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>postdoctoral_research</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>博士后</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>德国马克斯•普朗克分子生理所</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr"/>
+      <c r="I18" s="2" t="inlineStr"/>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr"/>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>机构名称和中点按源保留，不扩写或认定法律登记主体。；本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。；来源date_as_source：2017-2018</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr"/>
+      <c r="Q18" s="3" t="inlineStr">
+        <is>
+          <t>https://pharmacy.scu.edu.cn/info/1064/1823.htm</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>scu</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>四川大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>贾知军</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>employment</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>研究员</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>四川大学</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr"/>
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr"/>
+      <c r="I19" s="2" t="inlineStr"/>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr"/>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr"/>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>Preserve source wording; an open interval does not establish current employment at retrieval.；任职按留存来源表述保留；不据此认证当前人事状态。；来源date_as_source：2020-至今</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr"/>
+      <c r="Q19" s="3" t="inlineStr">
+        <is>
+          <t>https://pharmacy.scu.edu.cn/info/1064/1823.htm</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>scu</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>四川大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:S8"/>
+  <autoFilter ref="A1:S19"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q3" r:id="rId2"/>
@@ -1176,6 +1997,17 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q19" r:id="rId18"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1187,14 +2019,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="23.8" customWidth="1" min="2" max="2"/>
+    <col width="58.8" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="36.4" customWidth="1" min="5" max="5"/>
+    <col width="65" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="26.6" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
@@ -1428,12 +2260,318 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>宋振雷</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>涂永强</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>combined_masters_doctoral_stage_mentorship</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>硕博连读合并语境</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>师从；来源记载的关系；本轮未进行学位论文原件及导师当前人事认证。；仅一条合并阶段师承，不拆成两条，不认证正式学位论文导师。；原关系与阶段自述保留；未知不表示关系不存在，不建立现职身份导航。</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>https://pharmacy.scu.edu.cn/info/1058/1760.htm</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>scu</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>四川大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>宋振雷</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Richard. P Hsung</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>postdoctoral_stage_mentorship</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>博士后组合经历</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>师从；来源记载的关系；本轮未进行学位论文原件及导师当前人事认证。；姓名标点按源保留；同段两机构转移叙述未分配导师在各机构任职，不确认正式学位论文导师。；原关系与阶段自述保留；未知不表示关系不存在，不建立现职身份导航。</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>https://pharmacy.scu.edu.cn/info/1058/1760.htm</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>scu</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>四川大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>贾知军</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Herbert Waldmann</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>doctoral_stage_mentorship</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>博士</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>师从；来源记载的关系；本轮未进行学位论文原件及导师当前人事认证。；博士阶段师从，不升级为正式论文导师。；原关系与阶段自述保留；未知不表示关系不存在，不建立现职身份导航。</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr"/>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>https://pharmacy.scu.edu.cn/info/1064/1823.htm</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>scu</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>四川大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>贾知军</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>陈应春</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>masters_stage_mentorship</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>硕士</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>师从；来源记载的关系；本轮未进行学位论文原件及导师当前人事认证。；硕士阶段师从，不升级为正式论文导师。；原关系与阶段自述保留；未知不表示关系不存在，不建立现职身份导航。</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr"/>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>https://pharmacy.scu.edu.cn/info/1064/1823.htm</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>scu</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>四川大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>贾知军</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Frances H. Arnold</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>postdoctoral_stage_mentorship</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>博士后</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>师从；来源记载的关系；本轮未进行学位论文原件及导师当前人事认证。；博士后师从，不是学位论文指导关系。；原关系与阶段自述保留；未知不表示关系不存在，不建立现职身份导航。</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr"/>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>https://pharmacy.scu.edu.cn/info/1064/1823.htm</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>scu</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>四川大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>贾知军</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Herbert Waldmann</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>postdoctoral_stage_mentorship</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>博士后</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>师从；来源记载的关系；本轮未进行学位论文原件及导师当前人事认证。；与博士阶段为不同的明确阶段记录，非重复学位关系；导师身份不另展开。；原关系与阶段自述保留；未知不表示关系不存在，不建立现职身份导航。</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr"/>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>https://pharmacy.scu.edu.cn/info/1064/1823.htm</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>scu</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>四川大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L4"/>
+  <autoFilter ref="A1:L10"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I10" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1445,7 +2583,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1457,7 +2595,7 @@
     <col width="64.39999999999999" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="65" customWidth="1" min="9" max="9"/>
-    <col width="37.8" customWidth="1" min="10" max="10"/>
+    <col width="65" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
   </cols>
@@ -1632,13 +2770,229 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>宋振雷</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>有机化学</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D4" s="2" t="inlineStr"/>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>https://pharmacy.scu.edu.cn/info/1058/1760.htm</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>textbook_as_official_list</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>https://pharmacy.scu.edu.cn/info/1058/1760.htm</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；source_attributed_recovery_not_reverified</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；来源person_contribution_role_as_source：参编；来源书目信息（month）：8；来源书目信息（author_list_status）：No named author list supplied in selected official entry.；来源书目信息（edition_as_source）：版次9</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>scu</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>四川大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>宋振雷</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>“十二五”国家重点图书出版规划项目之中国科学发展战略：合成化学</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>2016</v>
+      </c>
+      <c r="D5" s="2" t="inlineStr"/>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>https://pharmacy.scu.edu.cn/info/1058/1760.htm</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>book_as_official_list</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>https://pharmacy.scu.edu.cn/info/1058/1760.htm</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；source_attributed_recovery_not_reverified</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；来源person_contribution_role_as_source：参编；来源书目信息（month）：1；来源书目信息（author_list_status）：No named author list supplied in selected official entry.；来源书目信息（title_limitation）：Entire title wording in source book brackets retained; series versus short title not independently separated.</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>scu</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>四川大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>贾知军</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Enzymatic Primary Amination of Benzylic and Allylic C(sp³)-H Bonds</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="D6" s="2" t="inlineStr"/>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>https://pharmacy.scu.edu.cn/info/1064/1823.htm</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>journal_article_as_official_list</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>https://pharmacy.scu.edu.cn/info/1064/1823.htm</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；source_attributed_recovery_not_reverified</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；来源authors_as_source：Jia, Z.-J.; Gao, S.; Arnold, F. H.；来源书目信息（author_list_status）：Full string as supplied in official entry; external completeness not verified.；来源书目信息（卷）：142；来源书目信息（页码）：10279−10283</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>scu</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>四川大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>贾知军</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Phosphine-Catalyzed Dearomatizing [3+2] Annulations of Isoquinolinium Methylides with Allenes</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>2015</v>
+      </c>
+      <c r="D7" s="2" t="inlineStr"/>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>https://pharmacy.scu.edu.cn/info/1064/1823.htm</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>journal_article_as_official_list</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>https://pharmacy.scu.edu.cn/info/1064/1823.htm</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；source_attributed_recovery_not_reverified</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；来源authors_as_source：Jia, Z.-J., Daniliuc, C. G., Antonchick, A. P.,* Waldmann, H.*；来源书目信息（author_list_status）：Full string as supplied in official entry; external completeness not verified.；来源书目信息（author_marker_note）：Asterisks and punctuation retained but not interpreted as correspondence or contribution roles.；来源书目信息（卷）：51；来源书目信息（页码）：1054-1057</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>scu</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>四川大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L3"/>
+  <autoFilter ref="A1:L7"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId12"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1650,14 +3004,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="29.4" customWidth="1" min="2" max="2"/>
+    <col width="64.39999999999999" customWidth="1" min="2" max="2"/>
     <col width="65" customWidth="1" min="3" max="3"/>
     <col width="65" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="33.59999999999999" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
@@ -1773,11 +3127,163 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>宋振雷</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>new-recovery-scu-songzhenlei-s001-b48a47b246af</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>https://pharmacy.scu.edu.cn/info/1058/1760.htm</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记录（本轮重新审查；非独立证书认证）；NEW_RECOVERY：依据留存来源摘录、摘要或结构化记录；除另有本轮证据说明外未重新读取原网页，不继承旧核验结论。</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T04:33:52.342Z</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>scu</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>四川大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>宋振雷</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>new-recovery-scu-songzhenlei-s002-26abb521bf58</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>https://pharmacy.scu.edu.cn/szdw1/szdw/ywhxx.htm</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记录（本轮重新审查；非独立证书认证）；NEW_RECOVERY：依据留存来源摘录、摘要或结构化记录；除另有本轮证据说明外未重新读取原网页，不继承旧核验结论。</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T04:34:02.436Z</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>scu</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>四川大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>贾知军</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>new-recovery-scu-jiazhijun-s001-d5771b88304e</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>https://pharmacy.scu.edu.cn/info/1064/1823.htm</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记录（本轮重新审查；非独立证书认证）；NEW_RECOVERY：依据留存来源摘录、摘要或结构化记录；除另有本轮证据说明外未重新读取原网页，不继承旧核验结论。</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T04:34:26.244Z</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>scu</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>四川大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>贾知军</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>new-recovery-scu-jiazhijun-s002-ce0a1cd4a752</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>https://pharmacy.scu.edu.cn/szdw1/szdw/swjsywxx.htm</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记录（本轮重新审查；非独立证书认证）；NEW_RECOVERY：依据留存来源摘录、摘要或结构化记录；除另有本轮证据说明外未重新读取原网页，不继承旧核验结论。</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T04:34:33.626Z</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>scu</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>四川大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G3"/>
+  <autoFilter ref="A1:G7"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/site/exports/scu-west-china-pharmacy.xlsx
+++ b/site/exports/scu-west-china-pharmacy.xlsx
@@ -1311,7 +1311,7 @@
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr"/>
@@ -1380,7 +1380,7 @@
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr"/>
@@ -1699,7 +1699,7 @@
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr"/>
@@ -1768,7 +1768,7 @@
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr"/>
